--- a/tables/testEDFA_ALL_LDD.xlsx
+++ b/tables/testEDFA_ALL_LDD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\greatuniter\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26F524E-F48D-42D2-A672-8381E7FC1235}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762FD88E-44F2-4F59-A491-6D677B39E653}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample" sheetId="1" r:id="rId1"/>
